--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -106,15 +106,24 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -142,12 +151,21 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>ITZEL</t>
   </si>
   <si>
@@ -175,16 +193,25 @@
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
     <t>LUCERO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,10 +1099,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1095,10 +1122,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1118,10 +1145,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1141,10 +1168,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1164,10 +1191,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1187,10 +1214,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1210,10 +1237,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1233,10 +1260,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1256,10 +1283,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1273,16 +1300,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920143</v>
+        <v>20330051920116</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1296,22 +1323,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920396</v>
+        <v>20330051920123</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1319,47 +1346,116 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920192</v>
+        <v>20330051920144</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>20330051920396</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
         <v>20330051920276</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>11</v>
       </c>
-      <c r="G14">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -91,6 +91,30 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
@@ -103,21 +127,6 @@
     <t>DE LUNA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>OJEDA</t>
   </si>
   <si>
@@ -127,7 +136,7 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>OLIVERA</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>ZACARIAS</t>
@@ -136,6 +145,30 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -148,28 +181,16 @@
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
   </si>
   <si>
     <t>SUSANA</t>
@@ -178,6 +199,33 @@
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
     <t>IVETTE</t>
   </si>
   <si>
@@ -188,24 +236,6 @@
   </si>
   <si>
     <t>EUDY</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
   <si>
     <t>KAREN YAZMIN</t>
@@ -804,16 +834,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>65.38</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -873,16 +906,19 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -964,16 +1000,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1042,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1061,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1093,16 +1129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920202</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1116,16 +1152,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920204</v>
+        <v>20330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,10 +1181,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1168,10 +1204,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1185,22 +1221,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920260</v>
+        <v>20330051920218</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1208,16 +1244,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1231,22 +1267,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920272</v>
+        <v>20330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1254,22 +1290,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19220030050208</v>
+        <v>20330051920123</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1277,22 +1313,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1300,22 +1336,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920116</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1323,22 +1359,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920123</v>
+        <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1346,22 +1382,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920144</v>
+        <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1369,16 +1405,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920396</v>
+        <v>20330051920329</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1392,22 +1428,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920192</v>
+        <v>20330051920260</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1415,16 +1451,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920276</v>
+        <v>20330051920270</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1438,24 +1474,93 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920143</v>
+        <v>20330051920272</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19220030050208</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920143</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G17">
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
@@ -100,91 +103,79 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>DE LA ROSA</t>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
+    <t>GABRIEL JOSUE</t>
   </si>
   <si>
     <t>REYNA ARISBETH</t>
@@ -211,37 +202,28 @@
     <t>EMELIN JIROMI</t>
   </si>
   <si>
-    <t>ALONDRA</t>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
   </si>
   <si>
     <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
   </si>
 </sst>
 </file>
@@ -811,16 +793,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -860,16 +845,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>57.89</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -883,16 +871,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>64.70999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -974,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>80.77</v>
+        <v>61.54</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1026,16 +1017,16 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1052,16 +1043,16 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1097,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,22 +1120,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920087</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1152,16 +1143,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920193</v>
+        <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,16 +1166,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920213</v>
+        <v>20330051920193</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1198,16 +1189,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1221,16 +1212,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920218</v>
+        <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1244,22 +1235,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920278</v>
+        <v>20330051920218</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1267,22 +1258,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920116</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1290,16 +1281,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920123</v>
+        <v>20330051920116</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1313,16 +1304,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920144</v>
+        <v>20330051920123</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1336,16 +1327,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920321</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1359,16 +1350,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1382,16 +1373,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1405,39 +1396,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920329</v>
+        <v>20330051920260</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920260</v>
+        <v>20330051920270</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1451,16 +1442,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1474,16 +1465,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1497,70 +1488,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19220030050208</v>
+        <v>20330051920321</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920276</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920143</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -79,70 +79,88 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>ROMANOS</t>
@@ -151,49 +169,46 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
     <t>DULCE FERNANDA</t>
   </si>
   <si>
     <t>SUSANA</t>
   </si>
   <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
-    <t>MARCO JOSAFAT</t>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
   </si>
   <si>
     <t>AMARANTA DENISSE</t>
@@ -202,25 +217,7 @@
     <t>EMELIN JIROMI</t>
   </si>
   <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
+    <t>ABDIEL</t>
   </si>
   <si>
     <t>SURISADAY</t>
@@ -650,10 +647,10 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -676,19 +673,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +699,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>17</v>
@@ -714,7 +711,7 @@
         <v>50</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,10 +816,10 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>17</v>
@@ -845,19 +842,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,19 +868,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,10 +985,10 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>17</v>
@@ -1000,7 +997,7 @@
         <v>65.38</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1014,19 +1011,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1040,10 +1037,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>23</v>
@@ -1052,7 +1049,7 @@
         <v>67.65000000000001</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,22 +1117,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920087</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1143,7 +1140,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920214</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1152,7 +1149,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1166,7 +1163,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920193</v>
+        <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1175,13 +1172,13 @@
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1189,7 +1186,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920213</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1198,13 +1195,13 @@
         <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1212,7 +1209,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1221,13 +1218,13 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1235,7 +1232,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920218</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1244,13 +1241,13 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1258,7 +1255,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>20330051920087</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1267,145 +1264,145 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920116</v>
+        <v>20330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920123</v>
+        <v>20330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920397</v>
+        <v>20330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920329</v>
+        <v>20330051920272</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920260</v>
+        <v>19220030050208</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1419,22 +1416,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920270</v>
+        <v>20330051920116</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1442,7 +1439,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920272</v>
+        <v>20330051920123</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
@@ -1451,13 +1448,13 @@
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1465,22 +1462,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19220030050208</v>
+        <v>20330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1491,13 +1488,13 @@
         <v>20330051920321</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -82,9 +82,15 @@
     <t>ASCENCION</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -100,15 +106,9 @@
     <t>MARROQUIN</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
@@ -127,9 +127,15 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -145,15 +151,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -175,9 +175,15 @@
     <t>REYNA ARISBETH</t>
   </si>
   <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
@@ -193,13 +199,7 @@
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
     <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
   </si>
   <si>
     <t>IVETTE</t>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920214</v>
+        <v>20330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920278</v>
+        <v>20330051920214</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1178,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920397</v>
+        <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920278</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1224,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920087</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1270,15 +1270,15 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1293,15 +1293,15 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920213</v>
+        <v>20330051920087</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1316,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920218</v>
+        <v>20330051920213</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1419,7 +1419,7 @@
         <v>20330051920116</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
@@ -1468,7 +1468,7 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>66</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>DE LA TEJA</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -182,6 +185,9 @@
   </si>
   <si>
     <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
@@ -1085,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1129,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,10 +1152,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,10 +1175,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1192,10 +1198,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1209,7 +1215,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>19330051920314</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1218,7 +1224,7 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1232,7 +1238,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1241,13 +1247,13 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1255,7 +1261,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920326</v>
+        <v>20330051920397</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1264,7 +1270,7 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1278,7 +1284,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1287,7 +1293,7 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1301,7 +1307,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920087</v>
+        <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1310,21 +1316,21 @@
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920213</v>
+        <v>20330051920087</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1333,13 +1339,13 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1347,7 +1353,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920260</v>
+        <v>20330051920213</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1356,13 +1362,13 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1370,7 +1376,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920272</v>
+        <v>20330051920260</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1379,7 +1385,7 @@
         <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1393,7 +1399,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19220030050208</v>
+        <v>20330051920272</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1402,7 +1408,7 @@
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1416,22 +1422,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920116</v>
+        <v>19220030050208</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1439,16 +1445,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920123</v>
+        <v>20330051920116</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1462,16 +1468,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920133</v>
+        <v>20330051920123</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1485,24 +1491,47 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>20330051920133</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>20330051920321</v>
       </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G18">
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -79,15 +79,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
@@ -97,93 +88,18 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
@@ -191,39 +107,6 @@
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
   </si>
   <si>
     <t>SURISADAY</t>
@@ -968,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -994,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1020,13 +903,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -1046,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -1072,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,16 +1006,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920218</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,22 +1029,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920193</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1169,22 +1052,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920214</v>
+        <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1192,346 +1075,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920218</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920314</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920278</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920397</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920326</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920329</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920087</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920213</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920260</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920272</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19220030050208</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920123</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920133</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
@@ -91,6 +100,15 @@
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -98,6 +116,15 @@
   </si>
   <si>
     <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>ALISSON FERNANDA</t>
@@ -974,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,16 +1033,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920218</v>
+        <v>20330051920196</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1029,22 +1056,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920200</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1052,22 +1079,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920278</v>
+        <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1075,24 +1102,93 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920314</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920278</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920321</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="G5">
+      <c r="G8">
         <v>1</v>
       </c>
     </row>
